--- a/artfynd/A 14188-2021 artfynd.xlsx
+++ b/artfynd/A 14188-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14188-2021 artfynd.xlsx
+++ b/artfynd/A 14188-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4897,6 +4897,113 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>115048555</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57239</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hustjärnen Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>404771</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7011775</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14188-2021 artfynd.xlsx
+++ b/artfynd/A 14188-2021 artfynd.xlsx
@@ -5009,7 +5009,7 @@
         <v>117720012</v>
       </c>
       <c r="B37" t="n">
-        <v>57398</v>
+        <v>57399</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
